--- a/docs/지방재정_데이터소스_점검표.xlsx
+++ b/docs/지방재정_데이터소스_점검표.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="범례" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'데이터소스 점검표'!$A$1:$I$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'데이터소스 점검표'!$A$1:$J$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -36,7 +36,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -68,6 +68,11 @@
         <fgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002F5496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -81,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -102,6 +107,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -467,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -479,6 +487,7 @@
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="38" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -527,6 +536,11 @@
           <t>주소</t>
         </is>
       </c>
+      <c r="J1" s="8" t="inlineStr">
+        <is>
+          <t>지속(계속 올라오나)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -546,17 +560,17 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>146종</t>
+          <t>146종 (전부 열림)</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>키 발급·146종 코드 전수 확보. 8종 실제 호출 성공. 243개 자치단체 전수 확인</t>
+          <t>146종 전부 호출 성공(2026-09-21). 공식 명세·출력 항목명 한글까지 확보. 243개 자치단체 전수. 일별 축 4종(QWGJK·HCFDA·SIHHC·WCEGCF)</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>인증키가 이 PC 에 없다 — .env 비어 있음. 키 없으면 한 쪽 5행 고정이라 전수 수집 불가. 일일 트래픽 제한은 여전히 실측 안 됨</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -566,12 +580,17 @@
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>예산·결산·재정지표 뼈대. QWGJK는 일별 집행</t>
+          <t>예산·결산·재정지표 뼈대. QWGJK 는 일별 집행, WCEGCF 계약현황에 업체명·수의계약·하도급까지 들어 있다</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
           <t>lofin365.go.kr</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>매일 도는 4종은 그날치까지 들어온다(2026-09 확인). 연 단위는 146종 중 129종이 살아 있고 17종은 2017~2022 에서 끊겼다 — 재정운용계획 8종(지방보조금·업무추진비·지방의회경비)이 2019 에서 멈춘 것이 아프다</t>
         </is>
       </c>
     </row>
@@ -613,12 +632,17 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>누가 계약을 따냈나 — 지방재정365에 없는 것</t>
+          <t>업체 대표자·사업자번호는 여기에만 있다. 계약 자체는 지방재정365 WCEGCF 에도 있음(2026-09-21 정정)</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
           <t>apis.data.go.kr/1230000/ao/CntrctInfoService</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>계약이 생길 때마다. 실측은 안 함</t>
         </is>
       </c>
     </row>
@@ -668,6 +692,11 @@
           <t>apis.data.go.kr/1741000/StanReginCd</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>행정구역이 바뀔 때만. 조인 키라 자주 바뀌면 곤란한 자료</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -715,6 +744,11 @@
           <t>apis.data.go.kr/1230000/as/ScsbidInfoService</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -762,6 +796,11 @@
           <t>apis.data.go.kr/1230000/ad/BidPublicInfoService</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -809,6 +848,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -856,6 +900,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>미확인 — GPT 확인 중</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -903,6 +952,11 @@
           <t>clik.nanet.go.kr</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>미확인 — GPT 확인 중</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -950,11 +1004,16 @@
           <t>openapi.openfiscaldata.go.kr/OPFI###  (WAF: 브라우저 User-Agent 필수)</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>적재주기 칸은 있으나 실측 안 함. 후순위로 내림(2026-09-21)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>미확인</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -969,32 +1028,37 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>34종 REST</t>
+          <t>통계 화면 39개</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>데이터셋 34건 목록 화면만 봄</t>
+          <t>2026-09-21 확인. 통합 OpenAPI 는 없다(공공데이터포털에 클린아이 오픈API 1건뿐, 나머지 23건은 파일데이터). 대신 화면이 서버에서 HTML 표로 그려져 로그인·키 없이 긁힌다. 부채·자산·자본·예산·부채비율·당기순이익 등 경영성과 화면에서 기관별 438곳 × 5개년(2021~2025)을 실제로 받아봤다. 엑셀 내려받기 단추도 있다</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>재무·부채 데이터가 API로 있는지. 인사데이터 위주로 보였음</t>
+          <t>39개 화면 중 재무는 9개쯤이고 나머지는 인사·보수다. 화면별 표 구조가 같은지 전수 확인 안 함. 자치단체 코드가 아니라 기관명으로만 나와서 지방재정365 와 잇는 조인 키가 없다 — 기관명 대조표를 만들어야 한다</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>필요 없음</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>지방공기업 88 + 출자출연기관 884</t>
+          <t>지방공기업 88 + 출자출연기관 884. 지방재정365 에는 비율만 있고 기관별 알맹이가 없다</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>cleaneye.go.kr</t>
+          <t>cleaneye.go.kr/user/fanScaleStat.do 등 39개</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>매년 경영공시 때 갱신. 2026-09 기준 화면에 2021~2025 다섯 해가 들어 있다 — 살아 있다. 다만 API 가 아니라 화면이라 개편되면 긁는 코드가 깨진다</t>
         </is>
       </c>
     </row>
@@ -1044,11 +1108,16 @@
           <t>eduinfo.go.kr</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>미확인 — GPT 확인 중</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>미확인</t>
+          <t>부분</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -1068,34 +1137,39 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>OpenAPI 존재. 키 1개로 전 서비스</t>
+          <t>2026-09-21 확인. 키 없이는 목록 API 부터 막힌다(err:11 유효하지않은 인증KEY). 익명 호출이 아예 안 된다</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>지방재정 통계가 몇 종인지</t>
+          <t>키를 받아야 무엇이 있는지 볼 수 있다. 다만 급하지 않다 — 1인당 계산에 쓸 인구는 지방재정365 HCDIB 가 자치단체별로 같이 준다(pptn_num, 243곳 전수, 합계 5,111만). 우선순위 내림</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>가입·발급 필요. 없음</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>인구 등 분모. 1인당 얼마 계산용</t>
+          <t>분모(인구)는 지방재정365 로 해결됨. KOSIS 는 그 밖의 지표가 필요해질 때</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
           <t>kosis.kr/openapi</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>미확인 (키가 없어 못 봄)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>미조사</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1110,39 +1184,44 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>2025년치만 10만 건 이상</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>시스템 존재. 대국민 공개 서비스 계획 언급</t>
+          <t>2026-09-21 확인. 로그인도 키도 없이 JSON 으로 열린다 — `/sp/aidBizInfoPbaInq` 에 POST {curPage, pageSize, bizYr, ...}. 한 행에 보조사업자명(pfmInstNm)·보조사업비(bizctSbatAmt)·자치단체코드(lafCd, 7자리로 지방재정365와 같은 키)·기관ID(pfmInstId)·공시일자가 들어 있다. CSV 내려받기 주소(/sp/aidBizInfoPbaCsvFIleDown)도 있다. 공모사업 선정결과(/sp/pbcnSlctnRsltInq)와 중요재산 정보공시도 같은 방식으로 열린다</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>API 여부 불명. ★보조금 수령 단체 명단이 여기 있을 수 있음</t>
+          <t>응답에 총건수 칸이 없어 쪽을 넘겨 세야 한다(2025년치가 10만~50만 건 사이). 사업자번호는 없고 이름만 나온다 — 같은 이름의 다른 단체를 가를 수 없다. pfmInstId 가 그 구실을 하는지 확인할 것. 교부 전 계획인지 집행 실적인지도 미확인</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>필요 없음</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>누가 보조금 받았나 — 시민단체 최대 관심사</t>
+          <t>누가 보조금 받았나 — 시민단체 최대 관심사. 자치단체코드가 같아서 지방재정365 예산·집행과 바로 이어붙일 수 있다</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>losims.go.kr</t>
+          <t>losims.go.kr/sp/aidBizInfoPba</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>살아 있다. 공시일자가 2026-09-14~18 로 최근 일주일치가 첫 쪽에 들어온다 — 날마다 올라온다는 뜻. 다만 API 가 아니라 화면 뒤 내부 호출이라 개편되면 깨진다</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>미조사</t>
+          <t>부분</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1162,12 +1241,12 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>지자체별 링크 허브로 보임</t>
+          <t>2026-09-21 확인. 전국 통합 데이터가 없다. 자치단체 이름을 넣으면 그 지자체의 주민참여예산 사이트로 보내 주는 게이트 화면이고, 나머지는 제도 소개·공지사항·자료실뿐이다. 공공데이터포털에 「주민참여예산」 오픈API 4건이 있으나 지자체가 따로 올린 것들이다</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>API 없을 가능성 높음</t>
+          <t>접었다. 전국 단위로 쓸 자료가 없다</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1177,19 +1256,24 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>주민참여예산 제안·채택 내역</t>
+          <t>주민참여예산 제안·채택 내역을 원했으나 여기엔 없다</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
           <t>pb.lofin365.go.kr</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>해당 없음</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>미조사</t>
+          <t>부분</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1209,12 +1293,12 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>웹 게시판 존재</t>
+          <t>2026-09-21 확인. 공공데이터포털에 감사원 오픈API 0건(파일데이터 6건뿐). 점검표에 적어 둔 추정이 맞았다 — API 가 없다</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>API 없고 PDF일 가능성 높음</t>
+          <t>게시판을 긁는 수밖에 없다. 본문이 PDF 면 그것도 어렵다. 지방재정365 LLBSR(교부세감액)로 일부 대체 가능하다는 판단은 그대로</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -1230,13 +1314,18 @@
       <c r="I16" s="3" t="inlineStr">
         <is>
           <t>bai.go.kr</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>미확인 (API 가 없어 판단 보류)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>미조사</t>
+          <t>부분</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1251,39 +1340,44 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>포털마다 제각각</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>서울 열린데이터광장·경기데이터드림 등 존재</t>
+          <t>2026-09-21 확인. 서울 열린데이터광장·경기데이터드림 둘 다 열린다. 다만 재정 자료는 API 가 아니라 시트·파일 위주다. 같은 자료가 공공데이터포털에도 모이는데 거기도 파일이 압도적이다 — 「예산」 4,454건 중 API 298건, 「재정」 3,483건 중 API 299건</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>중앙에 없는 세부 데이터가 있는지</t>
+          <t>전국 통일성이 없다는 게 결론이다. 243곳이 저마다 다른 포털에 다른 형식으로 올리고, 자체 포털이 아예 없는 기초단체가 많다. 뼈대로는 못 쓴다. 특정 광역을 깊이 팔 일이 생기면 그때 그 포털만 보는 게 맞다</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>포털마다 따로</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>광역 단위 심화. 전국 통일성은 없음</t>
+          <t>광역 단위 심화용. 243곳을 같은 잣대로 보는 데는 못 쓴다</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
           <t>data.seoul.go.kr 등</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>포털마다 다르고 파일데이터는 한 번 올리고 마는 것이 많다. 243곳 통일된 갱신을 기대할 수 없다 — 이것 때문에 뼈대에서 뺀다</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>미조사</t>
+          <t>부분</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1303,12 +1397,12 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>제도 존재</t>
+          <t>2026-09-21 확인. 공공데이터포털에 오픈API 0건, 파일데이터 3건뿐. 지방재정365 안에도 화면이 없다</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>공개 형태 전혀 모름</t>
+          <t>사실상 개방돼 있지 않다. 접는다</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -1324,13 +1418,18 @@
       <c r="I18" s="3" t="inlineStr">
         <is>
           <t>-</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>해당 없음</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>미조사</t>
+          <t>미확인</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1350,12 +1449,12 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>보고서 발간 기관</t>
+          <t>2026-09-21 확인. 공공데이터포털에 오픈API 6건이 있다(파일데이터는 0건)</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>데이터 개방 여부 모름</t>
+          <t>그 6건이 무엇인지 안 봄. 원천 데이터가 아니라 분석 자료일 가능성이 커서 후순위</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -1373,9 +1472,14 @@
           <t>nabo.go.kr</t>
         </is>
       </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I19"/>
+  <autoFilter ref="A1:J19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1386,7 +1490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1461,7 +1565,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-18. 확인할 때마다 갱신할 것</t>
+          <t>2026-09-18 작성 · 2026-09-21 대폭 갱신(지방재정365·클린아이·보탬e·KOSIS·주민e참여·감사원·투자심사·국회예산정책처), 지속 칸 추가</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>지속</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>자료가 계속 올라오는가. 한 번 받고 끝나는 자료는 사이트에 올려도 금방 죽는다</t>
         </is>
       </c>
     </row>

--- a/docs/지방재정_데이터소스_점검표.xlsx
+++ b/docs/지방재정_데이터소스_점검표.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="범례" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'데이터소스 점검표'!$A$1:$J$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'데이터소스 점검표'!$A$1:$K$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -488,6 +488,7 @@
     <col width="38" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
     <col width="46" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -541,6 +542,11 @@
           <t>지속(계속 올라오나)</t>
         </is>
       </c>
+      <c r="K1" s="8" t="inlineStr">
+        <is>
+          <t>확인자</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -593,6 +599,11 @@
           <t>매일 도는 4종은 그날치까지 들어온다(2026-09 확인). 연 단위는 146종 중 129종이 살아 있고 17종은 2017~2022 에서 끊겼다 — 재정운용계획 8종(지방보조금·업무추진비·지방의회경비)이 2019 에서 멈춘 것이 아프다</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Claude — 직접 호출해 봄</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -645,6 +656,11 @@
           <t>계약이 생길 때마다. 실측은 안 함</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Claude — 직접 호출해 봄</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -697,6 +713,11 @@
           <t>행정구역이 바뀔 때만. 조인 키라 자주 바뀌면 곤란한 자료</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Claude — 직접 호출해 봄</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -749,6 +770,11 @@
           <t>미확인</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Claude — 직접 호출해 봄</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -801,6 +827,11 @@
           <t>미확인</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Claude — 직접 호출해 봄</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -853,6 +884,11 @@
           <t>미확인</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>아직 아무도</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -905,6 +941,11 @@
           <t>미확인 — GPT 확인 중</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>GPT 맡음 (계정 필요) — 회신 대기</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -957,6 +998,11 @@
           <t>미확인 — GPT 확인 중</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>GPT 맡음 (계정 필요) — 회신 대기</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1009,6 +1055,11 @@
           <t>적재주기 칸은 있으나 실측 안 함. 후순위로 내림(2026-09-21)</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Claude — 직접 호출해 봄</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -1061,6 +1112,11 @@
           <t>매년 경영공시 때 갱신. 2026-09 기준 화면에 2021~2025 다섯 해가 들어 있다 — 살아 있다. 다만 API 가 아니라 화면이라 개편되면 긁는 코드가 깨진다</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Claude — 직접 호출해 봄</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1113,6 +1169,11 @@
           <t>미확인 — GPT 확인 중</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>GPT 맡음 (계정 필요) — 회신 대기</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1165,6 +1226,11 @@
           <t>미확인 (키가 없어 못 봄)</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Claude — 직접 호출해 봄</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -1217,6 +1283,11 @@
           <t>살아 있다. 공시일자가 2026-09-14~18 로 최근 일주일치가 첫 쪽에 들어온다 — 날마다 올라온다는 뜻. 다만 API 가 아니라 화면 뒤 내부 호출이라 개편되면 깨진다</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Claude — 직접 호출해 봄</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -1269,6 +1340,11 @@
           <t>해당 없음</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Claude — 직접 호출해 봄</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -1321,6 +1397,11 @@
           <t>미확인 (API 가 없어 판단 보류)</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Claude — 직접 호출해 봄</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -1373,6 +1454,11 @@
           <t>포털마다 다르고 파일데이터는 한 번 올리고 마는 것이 많다. 243곳 통일된 갱신을 기대할 수 없다 — 이것 때문에 뼈대에서 뺀다</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Claude — 직접 호출해 봄</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -1425,6 +1511,11 @@
           <t>해당 없음</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Claude — 직접 호출해 봄</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -1477,9 +1568,14 @@
           <t>미확인</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Claude — 직접 호출해 봄</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J19"/>
+  <autoFilter ref="A1:K19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1490,7 +1586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1557,6 +1653,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -1578,6 +1675,30 @@
       <c r="B8" t="inlineStr">
         <is>
           <t>자료가 계속 올라오는가. 한 번 받고 끝나는 자료는 사이트에 올려도 금방 죽는다</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>확인자</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>누가 확인했는지. 직접 호출해 본 것과 화면만 본 것은 신뢰도가 다르다</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>⚠ 인증키</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>키 값 자체는 이 파일에도 저장소에도 적지 않는다 — 공개 저장소다. 「있음/없음」만 적고 값은 .env 와 깃허브 Secrets 로만</t>
         </is>
       </c>
     </row>

--- a/docs/지방재정_데이터소스_점검표.xlsx
+++ b/docs/지방재정_데이터소스_점검표.xlsx
@@ -836,7 +836,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>미확인</t>
+          <t>부분</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -851,17 +851,17 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>1종</t>
+          <t>4종</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>활용신청 승인만</t>
+          <t>2026-09-21 확인. 물품·용역·공사·외자 4개 REST 호출 경로와 공식 명세를 확인했다</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>엔드포인트·내용 전부</t>
+          <t>승인키로 실제 호출을 안 했다. 계약상대자·계약금액·계약방식 등 실제 출력값을 봐야 한다</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -876,24 +876,24 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>data.go.kr/data/15129459/openapi.do</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>미확인</t>
+          <t>계약이 생길 때마다 올라오는 구조로 보이나 실측 안 함</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>아직 아무도</t>
+          <t>GPT — 공개 명세만 봄(실호출 없음)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>미확인</t>
+          <t>부분</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -908,17 +908,17 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>1종 (목록 3갈래)</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17 승인된 것 발견</t>
+          <t>2026-09-21 확인. 승인돼 있던 것은 「기획예산처_국고보조금 정보」(데이터 ID 15097584), REST 서비스다. 보조사업자정보공시목록에 보조사업자명·보조사업명·국고보조금 금액·회계연도·중앙부처명, 중요재산정보공시목록에 보조사업자명·중요재산명·계약 요청금액·현재가액·소재 시도, 보조사업현황에 교부처명·국고보조금·지자체부담금·자부담금이 있다</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>무슨 데이터인지 전혀. ★우선 확인</t>
+          <t>본체 API 를 발급키로 실제 호출하지 않았다. 최신 제공연도·누락·중복과 수령자 식별 품질(사업자번호가 있는지)은 아직 모른다</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -928,29 +928,29 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>국비가 어디로 갔나. 보조금 수령자 가능성</t>
+          <t>국비가 어디로 갔나. 보조사업자명 옆에 국고보조금·지자체부담금·자부담금이 같이 나와 보탬e(지방보조금)와 대칭으로 볼 수 있다</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>data.go.kr/data/15097584/openapi.do</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>미확인 — GPT 확인 중</t>
+          <t>연도별 자료 구조는 확인했으나 다년도 갱신 지속성은 실측 안 함</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>GPT 맡음 (계정 필요) — 회신 대기</t>
+          <t>GPT — 포털 목록 API 직접 호출·명세 확인. 본체는 미호출</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>미확인</t>
+          <t>부분</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -965,42 +965,42 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>4종</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Open API 존재. 1회 100건/1일 1,000회 제한</t>
+          <t>2026-09-21 확인. 공개 샘플키로 회의록·의안·의원·지방정책정보 4개 API 를 직접 호출했다. 공식 명세상 범위는 회의록 광역 17 + 기초 175, 의안·의원 광역 17 + 기초 125 곳. 회의록 상세에 안건·발언자·발언 전문 HTML·원본 파일 URL, 의안 상세에 제목·제안자·처리상태·위원회 및 본회의 결과·관련 파일이 있다. 예산·결산·보조금·수의계약·업무추진비·행정사무감사 본문 검색도 된다</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>API 목록 자체를 못 봄(로그인 필요)</t>
+          <t>사용자 인증키가 승인 대기다. 승인 뒤 사용자 키로 1건 호출해 보고, 명세에 적힌 의회가 실제로 다 최신 자료를 올리는지 확인해야 한다</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>없음 (신청 완료·승인 대기)</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>기초의회 회의록·의안·의원 — 감시 사이트의 차별점</t>
+          <t>기초의회 회의록·의안·의원 — 감시 사이트의 차별점. 숫자 옆에 그때 누가 무슨 말을 했는지를 붙일 수 있다</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>clik.nanet.go.kr</t>
+          <t>clik.nanet.go.kr/potal/guide/resourceCenter.do</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>미확인 — GPT 확인 중</t>
+          <t>회의록 API 에 2026-09-18 자료까지 들어온다 — 지금도 갱신 중. 의안·의원·정책정보의 갱신 지연은 실측 안 함</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>GPT 맡음 (계정 필요) — 회신 대기</t>
+          <t>GPT — 공개 샘플키로 4종 직접 호출해 봄</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>미확인</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1136,42 +1136,42 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>약 620종</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>OpenAPI 존재, SNS 가입 필요</t>
+          <t>2026-09-21 확인. 발급키로 실호출 성공. 예산통합공시 295종 · 결산통합공시 325종이고 대상은 17개 시·도교육청. 2024년 집행내역 2,220건에 보조사업명·보조사업자·보조금 집행액·최종정산액이 나온다</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>목록·내용 전부</t>
+          <t>620종의 과거 연도별 누락은 전수 검사 안 했다. 업무추진비 비율이 1% 미만에서 0 으로 잘리는 사례가 있어 원금액으로 다시 계산해야 한다. 학교운영비지원·운영비/인건비 재정결함지원·사립유치원지원은 교육청별 집계라 개별 학교명이 없고, 업무추진비·이월액·집행잔액도 교육청별 금액이다</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>17개 시도교육청. 기초 없어서 후순위</t>
+          <t>17개 시·도교육청. 기초가 없어 후순위지만, 보조사업자 이름이 실제로 나오는 몇 안 되는 소스다</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>eduinfo.go.kr</t>
+          <t>openapi.eduinfo.go.kr/openApi.do</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>미확인 — GPT 확인 중</t>
+          <t>연간 공시 구조. 2024년 자료 게시를 확인했다. 여러 해의 발표 시기·누락은 실측 안 함</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>GPT 맡음 (계정 필요) — 회신 대기</t>
+          <t>GPT — 발급키와 공개 샘플키로 실호출해 봄</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-18 작성 · 2026-09-21 대폭 갱신(지방재정365·클린아이·보탬e·KOSIS·주민e참여·감사원·투자심사·국회예산정책처), 지속 칸 추가</t>
+          <t>2026-09-18 작성 · 2026-09-21 대폭 갱신(지방재정365·클린아이·보탬e·KOSIS·주민e참여·감사원·투자심사·국회예산정책처), 지속 칸 추가 · 2026-09-21 GPT 회신분 반영(국고보조금·CLIK·지방교육재정알리미·계약과정통합공개)</t>
         </is>
       </c>
     </row>

--- a/docs/지방재정_데이터소스_점검표.xlsx
+++ b/docs/지방재정_데이터소스_점검표.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21 확인. 로그인도 키도 없이 JSON 으로 열린다 — `/sp/aidBizInfoPbaInq` 에 POST {curPage, pageSize, bizYr, ...}. 한 행에 보조사업자명(pfmInstNm)·보조사업비(bizctSbatAmt)·자치단체코드(lafCd, 7자리로 지방재정365와 같은 키)·기관ID(pfmInstId)·공시일자가 들어 있다. CSV 내려받기 주소(/sp/aidBizInfoPbaCsvFIleDown)도 있다. 공모사업 선정결과(/sp/pbcnSlctnRsltInq)와 중요재산 정보공시도 같은 방식으로 열린다</t>
+          <t>2026-09-21 확인. 로그인도 키도 없이 JSON 으로 열린다 — `/sp/aidBizInfoPbaInq` 에 POST {curPage, pageSize, bizYr}. 한 행에 보조사업자명(pfmInstNm)·보조사업비(bizctSbatAmt)·자치단체코드(lafCd)·기관ID(pfmInstId)·공시일자가 들어 있다. CSV 내려받기 주소(/sp/aidBizInfoPbaCsvFIleDown)도 있다. 공모사업 선정결과(/sp/pbcnSlctnRsltInq)와 중요재산 정보공시도 같은 방식으로 열린다. ★2026-09-21 재확인 — 응답 `input.totCnt` 에 총건수가 있다(2025년치 154,224건). 파이썬 urllib 은 SSL 핸드셰이크에서 막히고 curl 로는 된다</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>응답에 총건수 칸이 없어 쪽을 넘겨 세야 한다(2025년치가 10만~50만 건 사이). 사업자번호는 없고 이름만 나온다 — 같은 이름의 다른 단체를 가를 수 없다. pfmInstId 가 그 구실을 하는지 확인할 것. 교부 전 계획인지 집행 실적인지도 미확인</t>
+          <t>⚠️ 자치단체코드가 지방재정365와 다르다 — 보탬e 의 lafCd 4610000 이 「충청남도 예산군」인데 지방재정365 의 충남예산군은 4477000 이다. 바로 이어붙일 수 없고 기관명 대조표를 만들어야 한다(2026-09-21 정정. 그 전에 「같은 키」라고 적어 둔 것이 틀렸다). ⚠️ bizYr=2026 은 0건이다 — 지난해(2025)치가 최신이라 올해 벌어지는 사업은 여기서 못 본다. 요청 본문의 lafCd·bizNm 같은 거르개는 먹지 않는다(같은 결과가 온다) — 전수로 받아 우리 쪽에서 걸러야 한다. 사업자번호는 없고 이름만 나온다. pfmInstId 가 그 구실을 하는지 확인할 것. 교부 전 계획인지 집행 실적인지도 미확인</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1653,7 +1653,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>

--- a/docs/지방재정_데이터소스_점검표.xlsx
+++ b/docs/지방재정_데이터소스_점검표.xlsx
@@ -950,7 +950,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>부분</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -965,22 +965,22 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>4종</t>
+          <t>4종 · 목록 전수 2,166,011건</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21 확인. 공개 샘플키로 회의록·의안·의원·지방정책정보 4개 API 를 직접 호출했다. 공식 명세상 범위는 회의록 광역 17 + 기초 175, 의안·의원 광역 17 + 기초 125 곳. 회의록 상세에 안건·발언자·발언 전문 HTML·원본 파일 URL, 의안 상세에 제목·제안자·처리상태·위원회 및 본회의 결과·관련 파일이 있다. 예산·결산·보조금·수의계약·업무추진비·행정사무감사 본문 검색도 된다</t>
+          <t>2026-09-22 사용자 인증키로 4종 모두 실호출 성공. 목록 전수는 회의록 887,070 · 의안 756,667 · 의원 28,538 · 지방정책정보 493,736건(합 2,166,011). 의원 28,538건은 전수 확보, 나머지 셋은 각 16,700건까지 받아 뒀다. 명세가 로그인 없이 공개돼 있고(resourceCenter.do) 의회 코드표도 그 안에 있다. 자료는 30년치 — 회의록 1992년부터, 의안 1994년부터. [의원] PPRTY_NM 이 대수마다 반복되는 목록이라 쉼표를 세면 선수(選數)가 나온다 — 28,538명에 칸 43,448개, 3선 이상 3,461명, 최다 10선. 정당코드없음 44.7%는 자료 누락이 아니라 기초의원 정당공천(2006년) 이전이다 — 광역 3.3% 대 기초 56.6%로 갈린다. 명시적 무소속은 따로 6.7%. [의안] 제안자 칸으로 의원발의와 단체장발의를 가를 수 있다(시장 4,954 · 청도군수 1,308 …). 조례안 50.0% · 예산안/결산안 4.2%. [회의록] 회의명에 예산결산특별위원회가 5.2%(전수 4만 6천 건쯤). [정책정보] 자치단체 자료가 대부분이고 의정활동/감사자료가 13.8%. 게시일은 전부 성하다. 자세한 건 docs/CLIK_API_4종_명세.xlsx 와 README</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>사용자 인증키가 승인 대기다. 승인 뒤 사용자 키로 1건 호출해 보고, 명세에 적힌 의회가 실제로 다 최신 자료를 올리는지 확인해야 한다</t>
+          <t>⚠️ 하루 1,000회 · 한 번에 100건 한도. 목록 전수에 약 22일(21,661회). fetch_clik.py 를 날마다 돌려야 한다 — 이어받기는 된다. ⛔ 상세는 전수로 못 받는다(2,166일). 회의록의 값어치가 상세의 발언 전문에 있는데 그걸 다 못 받는 것이 핵심 제약이다. 예결위만 좁혀도 46일. 범위를 사용자가 정해야 한다. ⚠️ 쓰기 전에 손봐야 할 것 셋 — (1) 날짜 빈 값이 0 · 18000101 · 19000101 · 19700101 네 가지라 다 걸러야 한다(9자리 오타 11981124 도 봤다). (2) 의안상태 표기가 난립한다(같은 가결이 원안가결·처리-가결(원안)·가결·원안·원안의결 다섯 가지, 분류불가 12.8%) — 정규화가 먼저다. (3) 회의명이 기타 24.9% · "-" 7.3% 로 3할이 비었고 한자 표기(本會議)도 섞였다. ⚠️ 정책정보는 수집된 곳이 47곳뿐이고 제주·인천이 45.6%라 243곳 비교에는 못 쓴다. 정렬 인자가 없어 수집 도중 쪽이 밀리니 다 받은 뒤 한 번 더 훑을 것. ⚠️ 회의록 searchType=PRMPST_CMIT_NM(위원회명)은 명세에 있는데 ERROR06 으로 막힌다. 한도를 올릴 수 있는지는 안 물어봤다(02-6788-4367 / clik@nanet.go.kr).</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>없음 (신청 완료·승인 대기)</t>
+          <t>있음 (.env 의 CLIK_KEY · 값은 저장소에 안 적는다)</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -995,12 +995,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>회의록 API 에 2026-09-18 자료까지 들어온다 — 지금도 갱신 중. 의안·의원·정책정보의 갱신 지연은 실측 안 함</t>
+          <t>살아 있다 — 2026-09-18 자 회의록·의안이 들어온다. 의원은 대수(10대)까지 붙어 오고, 정책정보는 2026-07 까지 확인</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>GPT — 공개 샘플키로 4종 직접 호출해 봄</t>
+          <t>Claude — 사용자 키로 4종 실호출, 의원 28,538건 전수 + 나머지 셋 각 16,700건 받아서 내용까지 세어 봄(2026-09-22)</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-18 작성 · 2026-09-21 대폭 갱신(지방재정365·클린아이·보탬e·KOSIS·주민e참여·감사원·투자심사·국회예산정책처), 지속 칸 추가 · 2026-09-21 GPT 회신분 반영(국고보조금·CLIK·지방교육재정알리미·계약과정통합공개)</t>
+          <t>2026-09-18 작성 · 2026-09-21 대폭 갱신(지방재정365·클린아이·보탬e·KOSIS·주민e참여·감사원·투자심사·국회예산정책처), 지속 칸 추가 · 2026-09-21 GPT 회신분 반영(국고보조금·CLIK·지방교육재정알리미·계약과정통합공개) · 2026-09-22 저녁 CLIK 완료 반영(Claude)</t>
         </is>
       </c>
     </row>

--- a/docs/지방재정_데이터소스_점검표.xlsx
+++ b/docs/지방재정_데이터소스_점검표.xlsx
@@ -1037,7 +1037,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>있음 (저장소 Secrets 의 OPENFISCAL_KEY · 2026-09-22 넣음). ⚠️ .env 에는 아직 빈 칸이라 손으로 돌릴 때는 못 쓴다</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
